--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T14:16:19+00:00</t>
+    <t>2025-02-13T08:25:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-specimen.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1734" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="352">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T08:25:30+00:00</t>
+    <t>2025-02-13T08:54:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1070,7 +1070,29 @@
     <t>http://terminology.hl7.org/ValueSet/v2-0493</t>
   </si>
   <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>SPM-24</t>
+  </si>
+  <si>
+    <t>Specimen.condition:insufficientsample</t>
+  </si>
+  <si>
+    <t>insufficientsample</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="http://snomed.info/sct"/&gt;
+    &lt;code value="281268007"/&gt;
+    &lt;display value="Insufficient sample (finding)"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Specimen.note</t>
@@ -1388,12 +1410,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM49"/>
+  <dimension ref="A1:AM50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="37.796875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="37.796875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.82421875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -6689,16 +6711,14 @@
         <v>76</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC48" t="s" s="2">
-        <v>76</v>
-      </c>
+        <v>341</v>
+      </c>
+      <c r="AC48" s="2"/>
       <c r="AD48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>76</v>
+        <v>342</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>334</v>
@@ -6722,17 +6742,19 @@
         <v>76</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>334</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="D49" t="s" s="2">
         <v>76</v>
       </c>
@@ -6741,7 +6763,7 @@
         <v>77</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>76</v>
@@ -6750,19 +6772,23 @@
         <v>76</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>343</v>
+        <v>164</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>50</v>
+        <v>335</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>76</v>
       </c>
@@ -6771,7 +6797,7 @@
         <v>76</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>76</v>
+        <v>346</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>76</v>
@@ -6786,13 +6812,13 @@
         <v>76</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>76</v>
+        <v>168</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>76</v>
+        <v>339</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>76</v>
+        <v>340</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>76</v>
@@ -6810,7 +6836,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -6825,13 +6851,122 @@
         <v>96</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>345</v>
+        <v>76</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>351</v>
       </c>
     </row>
   </sheetData>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-13T08:54:32+00:00</t>
+    <t>2025-02-14T08:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T08:32:04+00:00</t>
+    <t>2025-02-14T09:49:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-14T09:49:00+00:00</t>
+    <t>2025-02-17T15:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T15:20:00+00:00</t>
+    <t>2025-02-18T09:36:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-specimen.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/StructureDefinition-at-aps-specimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T09:36:51+00:00</t>
+    <t>2025-02-21T10:11:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
